--- a/tests/fixtures/banks/shinhan_sample.xlsx
+++ b/tests/fixtures/banks/shinhan_sample.xlsx
@@ -419,22 +419,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>날짜</t>
+          <t>거래일시</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>시간</t>
+          <t>적요</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>적요</t>
+          <t>출금액</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>금액</t>
+          <t>입금액</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -491,22 +491,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-01 09:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>급여지급</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>급여지급</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>-3200000</t>
+          <t>3200000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,22 +543,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-02 09:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>전기요금납부</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>수도요금납부</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-88000</t>
+          <t>88000</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -605,22 +595,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-03 09:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>차량수리비</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>차량유지비</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>-65000</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -638,11 +623,7 @@
           <t>이체</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>GS칼텍스</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>111-222</t>
@@ -662,16 +643,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-04 09:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>매출수입</t>
         </is>
       </c>
@@ -697,7 +673,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>고객사ABC</t>
+          <t>고객사</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,22 +695,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-05 09:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>이상거래XYZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>이상거래XYZ</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>-5000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
